--- a/data/propiedades.xlsx
+++ b/data/propiedades.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE6AABD-A8BF-4BB9-BE6F-50FE6FA24ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863F0CE0-BEC8-4D9A-A6B6-07F27719284A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="582">
   <si>
     <t>ID</t>
   </si>
@@ -197,24 +197,12 @@
     <t>Residencia doble cerca del Malecon con 6 recamaras, alberca, gimnasio. Oportunidad unica.</t>
   </si>
   <si>
-    <t>Casa Velero — Altavela</t>
-  </si>
-  <si>
-    <t>$3,035,000</t>
-  </si>
-  <si>
     <t>Altavela Residencial, La Paz</t>
   </si>
   <si>
     <t>Av. La Cima</t>
   </si>
   <si>
-    <t>$1,800/mes</t>
-  </si>
-  <si>
-    <t>Modelo Velero, casa disenada para brindar seguridad y modernidad en Altavela Residencial.</t>
-  </si>
-  <si>
     <t>Casa Puerta Cortez</t>
   </si>
   <si>
@@ -329,18 +317,6 @@
     <t>Ideal para familias que buscan su primer hogar. Residencial Altamira en Miramar.</t>
   </si>
   <si>
-    <t>Casa San Jorge — San Rafael</t>
-  </si>
-  <si>
-    <t>$3,080,000</t>
-  </si>
-  <si>
-    <t>Av. Bahia Grande</t>
-  </si>
-  <si>
-    <t>Modelo San Jorge en Residencial San Rafael. Entorno residencial seguro y tranquilo.</t>
-  </si>
-  <si>
     <t>Casa Punta Arena</t>
   </si>
   <si>
@@ -566,18 +542,6 @@
     <t>Villa de lujo con alberca privada y vista al mar en Pedregal La Paz.</t>
   </si>
   <si>
-    <t>Mar de Plata Modelo Golfo</t>
-  </si>
-  <si>
-    <t>$8,900,000</t>
-  </si>
-  <si>
-    <t>Calle de acceso</t>
-  </si>
-  <si>
-    <t>Residencia de lujo en privada frente al mar con vistas espectaculares al Mar de Cortes.</t>
-  </si>
-  <si>
     <t>Casa Privada Santa Julia 2</t>
   </si>
   <si>
@@ -1070,21 +1034,9 @@
     <t>Altavela Residencial</t>
   </si>
   <si>
-    <t>Velero</t>
-  </si>
-  <si>
-    <t>No disponible por modelo (rango general del desarrollo: $2,819,900 – $4,794,000 MXN)</t>
-  </si>
-  <si>
     <t>Altavela Residencial, La Paz, BCS</t>
   </si>
   <si>
-    <t>169.35 m²</t>
-  </si>
-  <si>
-    <t>103.35 m²</t>
-  </si>
-  <si>
     <t>Pincali</t>
   </si>
   <si>
@@ -1773,6 +1725,54 @@
   </si>
   <si>
     <t>Tribuna de México</t>
+  </si>
+  <si>
+    <t>URL Imagen</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/48/92/61/90/1200x1200/1587104686.jpg?isFirstImage=true</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/48/92/61/90/1200x1200/1587104692.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/48/92/61/90/1200x1200/1587104688.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/10/76/67/1200x1200/1590644718.jpg?isFirstImage=true</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/10/76/67/1200x1200/1590644703.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/10/76/67/1200x1200/1590644705.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/74/11/45/1200x1200/1603847351.jpg?isFirstImage=true</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/18/01/49/74/11/45/360x266/1603847365.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/74/11/45/1200x1200/1603847334.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/50/67/61/67/1200x1200/1623184900.jpg?isFirstImage=true</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/50/67/61/67/1200x1200/1623184901.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/50/67/61/67/1200x1200/1623184902.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/65/28/67/1200x1200/1602057090.jpg?isFirstImage=true</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/18/01/49/65/28/67/360x266/1602057077.jpg</t>
+  </si>
+  <si>
+    <t>https://img10.naventcdn.com/avisos/resize/18/01/49/65/28/67/1200x1200/1602057083.jpg</t>
   </si>
 </sst>
 </file>
@@ -1782,7 +1782,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1835,6 +1835,14 @@
       <color rgb="FF0A4C5C"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1854,7 +1862,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1877,11 +1885,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1902,9 +1939,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1929,8 +1964,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1947,8 +2006,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9E34C9D6-550D-4F1E-8D72-5CAE1DE8A318}" name="ViviendasLaPaz" displayName="ViviendasLaPaz" ref="A4:L68">
-  <autoFilter ref="A4:L68" xr:uid="{9E34C9D6-550D-4F1E-8D72-5CAE1DE8A318}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9E34C9D6-550D-4F1E-8D72-5CAE1DE8A318}" name="ViviendasLaPaz" displayName="ViviendasLaPaz" ref="A4:L67">
+  <autoFilter ref="A4:L67" xr:uid="{9E34C9D6-550D-4F1E-8D72-5CAE1DE8A318}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{4605612A-F80B-40B1-BE13-188FEA0D610E}" name="Categoría"/>
     <tableColumn id="2" xr3:uid="{ABBD1325-05A6-4B75-89C5-613B846C6E84}" name="Desarrollo"/>
@@ -2289,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2303,10 +2362,12 @@
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="45" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" style="8" customWidth="1"/>
+    <col min="17" max="17" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2349,11 +2410,16 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P1" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+    </row>
+    <row r="2" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2394,14 +2460,23 @@
         <v>21</v>
       </c>
       <c r="N2" s="6">
-        <f t="shared" ref="N2:N33" si="0">IFERROR(C2/H2,0)</f>
+        <f t="shared" ref="N2:N31" si="0">IFERROR(C2/H2,0)</f>
         <v>21586.907983761841</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="23" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P2" s="27" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2448,8 +2523,17 @@
       <c r="O3" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P3" s="26" t="s">
+        <v>570</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="R3" s="20" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2496,8 +2580,17 @@
       <c r="O4" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P4" s="26" t="s">
+        <v>573</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2544,8 +2637,17 @@
       <c r="O5" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P5" s="26" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2592,8 +2694,17 @@
       <c r="O6" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P6" s="26" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q6" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="R6" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2640,8 +2751,9 @@
       <c r="O7" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P7" s="21"/>
+    </row>
+    <row r="8" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2688,316 +2800,323 @@
       <c r="O8" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P8" s="21"/>
+    </row>
+    <row r="9" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4">
-        <v>3035000</v>
+        <v>20589400</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="I9" s="2">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2">
         <v>3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>2</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>21678.571428571428</v>
+        <v>103986.86868686869</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P9" s="21"/>
+    </row>
+    <row r="10" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10" s="4">
-        <v>20589400</v>
+        <v>4490000</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H10" s="2">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="I10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="2">
         <v>3</v>
       </c>
       <c r="K10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>103986.86868686869</v>
+        <v>28062.5</v>
       </c>
       <c r="O10" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="P10" s="21"/>
+    </row>
+    <row r="11" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="4">
-        <v>4490000</v>
+        <v>44908600</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" s="2">
-        <v>160</v>
+        <v>594</v>
       </c>
       <c r="I11" s="2">
+        <v>4</v>
+      </c>
+      <c r="J11" s="2">
+        <v>5</v>
+      </c>
+      <c r="K11" s="2">
         <v>3</v>
       </c>
-      <c r="J11" s="2">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>28062.5</v>
+        <v>75603.703703703708</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P11" s="21"/>
+    </row>
+    <row r="12" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="4">
-        <v>44908600</v>
+        <v>5200000</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" s="2">
-        <v>594</v>
+        <v>500</v>
       </c>
       <c r="I12" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N12" s="6">
         <f t="shared" si="0"/>
-        <v>75603.703703703708</v>
+        <v>10400</v>
       </c>
       <c r="O12" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P12" s="21"/>
+    </row>
+    <row r="13" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4">
-        <v>5200000</v>
+        <v>8837460</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H13" s="2">
-        <v>500</v>
+        <v>198</v>
       </c>
       <c r="I13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2">
         <v>2</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N13" s="6">
         <f t="shared" si="0"/>
-        <v>10400</v>
+        <v>44633.63636363636</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P13" s="21"/>
+    </row>
+    <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C14" s="4">
-        <v>8837460</v>
+        <v>2819900</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="H14" s="2">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="I14" s="2">
         <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2">
         <v>2</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="N14" s="6">
         <f t="shared" si="0"/>
-        <v>44633.63636363636</v>
+        <v>20142.142857142859</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P14" s="21"/>
+    </row>
+    <row r="15" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1519900</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="C15" s="4">
-        <v>2819900</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2">
         <v>140</v>
@@ -3006,97 +3125,99 @@
         <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N15" s="6">
         <f t="shared" si="0"/>
-        <v>20142.142857142859</v>
+        <v>10856.428571428571</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P15" s="21"/>
+    </row>
+    <row r="16" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" s="4">
-        <v>1519900</v>
+        <v>5800000</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="I16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N16" s="6">
         <f t="shared" si="0"/>
-        <v>10856.428571428571</v>
+        <v>34319.526627218933</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P16" s="21"/>
+    </row>
+    <row r="17" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C17" s="4">
-        <v>3080000</v>
+        <v>4950000</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="I17" s="2">
         <v>3</v>
@@ -3105,94 +3226,96 @@
         <v>2</v>
       </c>
       <c r="K17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N17" s="6">
         <f t="shared" si="0"/>
-        <v>23875.968992248061</v>
+        <v>24750</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P17" s="21"/>
+    </row>
+    <row r="18" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C18" s="4">
-        <v>5800000</v>
+        <v>4500000</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2">
-        <v>169</v>
+        <v>240</v>
       </c>
       <c r="I18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N18" s="6">
         <f t="shared" si="0"/>
-        <v>34319.526627218933</v>
+        <v>18750</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P18" s="21"/>
+    </row>
+    <row r="19" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4">
-        <v>4950000</v>
+        <v>3800000</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="I19" s="2">
         <v>3</v>
@@ -3204,79 +3327,81 @@
         <v>2</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N19" s="6">
         <f t="shared" si="0"/>
-        <v>24750</v>
+        <v>27941.176470588234</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P19" s="21"/>
+    </row>
+    <row r="20" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="4">
-        <v>4500000</v>
+        <v>2700000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2">
         <v>2</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N20" s="6">
         <f t="shared" si="0"/>
-        <v>18750</v>
+        <v>19285.714285714286</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P20" s="21"/>
+    </row>
+    <row r="21" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="4">
+        <v>4050000</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3800000</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>25</v>
@@ -3285,67 +3410,68 @@
         <v>42</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="H21" s="2">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="I21" s="2">
         <v>3</v>
       </c>
       <c r="J21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="N21" s="6">
         <f t="shared" si="0"/>
-        <v>27941.176470588234</v>
+        <v>27000</v>
       </c>
       <c r="O21" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P21" s="21"/>
+    </row>
+    <row r="22" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="4">
+        <v>11500000</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C22" s="4">
-        <v>2700000</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="H22" s="2">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="I22" s="2">
+        <v>4</v>
+      </c>
+      <c r="J22" s="2">
+        <v>3</v>
+      </c>
+      <c r="K22" s="2">
         <v>2</v>
-      </c>
-      <c r="J22" s="2">
-        <v>2</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>20</v>
@@ -3355,45 +3481,46 @@
       </c>
       <c r="N22" s="6">
         <f t="shared" si="0"/>
-        <v>19285.714285714286</v>
+        <v>19166.666666666668</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P22" s="21"/>
+    </row>
+    <row r="23" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C23" s="4">
-        <v>4050000</v>
+        <v>19878100</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>127</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="I23" s="2">
         <v>3</v>
       </c>
       <c r="J23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
@@ -3403,21 +3530,22 @@
       </c>
       <c r="N23" s="6">
         <f t="shared" si="0"/>
-        <v>27000</v>
+        <v>82481.742738589208</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P23" s="21"/>
+    </row>
+    <row r="24" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C24" s="4">
-        <v>11500000</v>
+        <v>3130000</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>131</v>
@@ -3426,19 +3554,19 @@
         <v>25</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>132</v>
       </c>
       <c r="H24" s="2">
-        <v>600</v>
+        <v>122</v>
       </c>
       <c r="I24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2">
         <v>2</v>
@@ -3451,39 +3579,40 @@
       </c>
       <c r="N24" s="6">
         <f t="shared" si="0"/>
-        <v>19166.666666666668</v>
+        <v>25655.737704918032</v>
       </c>
       <c r="O24" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P24" s="21"/>
+    </row>
+    <row r="25" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C25" s="4">
-        <v>19878100</v>
+        <v>2616000</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>135</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="H25" s="2">
-        <v>241</v>
+        <v>140</v>
       </c>
       <c r="I25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2">
         <v>2</v>
@@ -3499,21 +3628,22 @@
       </c>
       <c r="N25" s="6">
         <f t="shared" si="0"/>
-        <v>82481.742738589208</v>
+        <v>18685.714285714286</v>
       </c>
       <c r="O25" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P25" s="21"/>
+    </row>
+    <row r="26" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>138</v>
       </c>
       <c r="C26" s="4">
-        <v>3130000</v>
+        <v>3950000</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>139</v>
@@ -3522,22 +3652,22 @@
         <v>25</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H26" s="2">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="I26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2">
         <v>2</v>
       </c>
       <c r="K26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>20</v>
@@ -3547,183 +3677,187 @@
       </c>
       <c r="N26" s="6">
         <f t="shared" si="0"/>
-        <v>25655.737704918032</v>
+        <v>17173.91304347826</v>
       </c>
       <c r="O26" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P26" s="21"/>
+    </row>
+    <row r="27" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C27" s="4">
-        <v>2616000</v>
+        <v>40170600</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>143</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H27" s="2">
-        <v>140</v>
+        <v>1261</v>
       </c>
       <c r="I27" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K27" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N27" s="6">
         <f t="shared" si="0"/>
-        <v>18685.714285714286</v>
+        <v>31856.145915939731</v>
       </c>
       <c r="O27" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P27" s="21"/>
+    </row>
+    <row r="28" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C28" s="4">
-        <v>3950000</v>
+        <v>4850000</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H28" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I28" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J28" s="2">
+        <v>3</v>
+      </c>
+      <c r="K28" s="2">
         <v>2</v>
-      </c>
-      <c r="K28" s="2">
-        <v>3</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N28" s="6">
         <f t="shared" si="0"/>
-        <v>17173.91304347826</v>
+        <v>20726.495726495727</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P28" s="21"/>
+    </row>
+    <row r="29" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C29" s="4">
-        <v>40170600</v>
+        <v>2475000</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H29" s="2">
-        <v>1261</v>
+        <v>160</v>
       </c>
       <c r="I29" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J29" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N29" s="6">
         <f t="shared" si="0"/>
-        <v>31856.145915939731</v>
+        <v>15468.75</v>
       </c>
       <c r="O29" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P29" s="21"/>
+    </row>
+    <row r="30" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C30" s="4">
-        <v>4850000</v>
+        <v>7700000</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H30" s="2">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="I30" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2">
         <v>3</v>
@@ -3735,49 +3869,50 @@
         <v>20</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N30" s="6">
         <f t="shared" si="0"/>
-        <v>20726.495726495727</v>
+        <v>28000</v>
       </c>
       <c r="O30" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P30" s="21"/>
+    </row>
+    <row r="31" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="4">
-        <v>2475000</v>
+        <v>3877000</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>163</v>
+        <v>42</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>164</v>
       </c>
       <c r="H31" s="2">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="I31" s="2">
         <v>3</v>
       </c>
       <c r="J31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>20</v>
@@ -3787,21 +3922,22 @@
       </c>
       <c r="N31" s="6">
         <f t="shared" si="0"/>
-        <v>15468.75</v>
+        <v>28507.352941176472</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P31" s="21"/>
+    </row>
+    <row r="32" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C32" s="4">
-        <v>7700000</v>
+        <v>15500000</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>167</v>
@@ -3810,16 +3946,16 @@
         <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H32" s="2">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="I32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="2">
         <v>3</v>
@@ -3831,28 +3967,29 @@
         <v>20</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N32" s="6">
-        <f t="shared" si="0"/>
-        <v>28000</v>
+        <f t="shared" ref="N32:N54" si="1">IFERROR(C32/H32,0)</f>
+        <v>93939.393939393936</v>
       </c>
       <c r="O32" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P32" s="21"/>
+    </row>
+    <row r="33" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C33" s="4">
-        <v>3877000</v>
+        <v>3300000</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>25</v>
@@ -3861,19 +3998,19 @@
         <v>42</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="H33" s="2">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="I33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2">
         <v>2</v>
       </c>
       <c r="K33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>20</v>
@@ -3882,22 +4019,23 @@
         <v>173</v>
       </c>
       <c r="N33" s="6">
-        <f t="shared" si="0"/>
-        <v>28507.352941176472</v>
+        <f t="shared" si="1"/>
+        <v>22000</v>
       </c>
       <c r="O33" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P33" s="21"/>
+    </row>
+    <row r="34" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C34" s="4">
-        <v>15500000</v>
+        <v>2400000</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>175</v>
@@ -3912,16 +4050,16 @@
         <v>177</v>
       </c>
       <c r="H34" s="2">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="I34" s="2">
         <v>3</v>
       </c>
       <c r="J34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>20</v>
@@ -3930,412 +4068,421 @@
         <v>178</v>
       </c>
       <c r="N34" s="6">
-        <f t="shared" ref="N34:N57" si="1">IFERROR(C34/H34,0)</f>
-        <v>93939.393939393936</v>
+        <f t="shared" si="1"/>
+        <v>10000</v>
       </c>
       <c r="O34" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P34" s="21"/>
+    </row>
+    <row r="35" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C35" s="4">
-        <v>8900000</v>
+        <v>14401420</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>180</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H35" s="2">
-        <v>322</v>
+        <v>1560</v>
       </c>
       <c r="I35" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K35" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N35" s="6">
         <f t="shared" si="1"/>
-        <v>27639.751552795031</v>
+        <v>9231.6794871794864</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P35" s="21"/>
+    </row>
+    <row r="36" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" s="4">
-        <v>3300000</v>
+        <v>30000000</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="H36" s="2">
-        <v>150</v>
+        <v>425</v>
       </c>
       <c r="I36" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J36" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K36" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N36" s="6">
         <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>70588.23529411765</v>
       </c>
       <c r="O36" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P36" s="21"/>
+    </row>
+    <row r="37" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C37" s="4">
-        <v>2400000</v>
+        <v>3700000</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H37" s="2">
-        <v>240</v>
+        <v>404</v>
       </c>
       <c r="I37" s="2">
         <v>3</v>
       </c>
       <c r="J37" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N37" s="6">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>9158.4158415841575</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P37" s="21"/>
+    </row>
+    <row r="38" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C38" s="4">
-        <v>14401420</v>
+        <v>2200000</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>71</v>
+        <v>195</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H38" s="2">
-        <v>1560</v>
+        <v>105</v>
       </c>
       <c r="I38" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J38" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K38" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N38" s="6">
         <f t="shared" si="1"/>
-        <v>9231.6794871794864</v>
+        <v>20952.380952380954</v>
       </c>
       <c r="O38" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P38" s="21"/>
+    </row>
+    <row r="39" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C39" s="4">
-        <v>30000000</v>
+        <v>3470000</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H39" s="2">
-        <v>425</v>
+        <v>154</v>
       </c>
       <c r="I39" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J39" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K39" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N39" s="6">
         <f t="shared" si="1"/>
-        <v>70588.23529411765</v>
+        <v>22532.467532467534</v>
       </c>
       <c r="O39" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P39" s="21"/>
+    </row>
+    <row r="40" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C40" s="4">
-        <v>3700000</v>
+        <v>43238020</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H40" s="2">
-        <v>404</v>
+        <v>2173</v>
       </c>
       <c r="I40" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J40" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K40" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N40" s="6">
         <f t="shared" si="1"/>
-        <v>9158.4158415841575</v>
+        <v>19897.846295444087</v>
       </c>
       <c r="O40" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P40" s="21"/>
+    </row>
+    <row r="41" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C41" s="4">
-        <v>2200000</v>
+        <v>2616000</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>207</v>
+        <v>42</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="H41" s="2">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="I41" s="2">
         <v>2</v>
       </c>
       <c r="J41" s="2">
+        <v>2</v>
+      </c>
+      <c r="K41" s="2">
         <v>1</v>
-      </c>
-      <c r="K41" s="2">
-        <v>2</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="1"/>
-        <v>20952.380952380954</v>
+        <v>18820.143884892088</v>
       </c>
       <c r="O41" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P41" s="21"/>
+    </row>
+    <row r="42" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C42" s="4">
-        <v>3470000</v>
+        <v>11000000</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H42" s="2">
-        <v>154</v>
+        <v>406</v>
       </c>
       <c r="I42" s="2">
         <v>3</v>
       </c>
       <c r="J42" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2">
         <v>3</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" s="6">
         <f t="shared" si="1"/>
-        <v>22532.467532467534</v>
+        <v>27093.596059113301</v>
       </c>
       <c r="O42" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P42" s="21"/>
+    </row>
+    <row r="43" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C43" s="4">
-        <v>43238020</v>
+        <v>3990000</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>218</v>
+        <v>25</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>219</v>
@@ -4344,16 +4491,16 @@
         <v>220</v>
       </c>
       <c r="H43" s="2">
-        <v>2173</v>
+        <v>924</v>
       </c>
       <c r="I43" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J43" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>20</v>
@@ -4363,138 +4510,141 @@
       </c>
       <c r="N43" s="6">
         <f t="shared" si="1"/>
-        <v>19897.846295444087</v>
+        <v>4318.181818181818</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P43" s="21"/>
+    </row>
+    <row r="44" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C44" s="4">
-        <v>2616000</v>
+        <v>8790000</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>42</v>
+        <v>224</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="H44" s="2">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="I44" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" s="2">
         <v>2</v>
       </c>
       <c r="K44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N44" s="6">
         <f t="shared" si="1"/>
-        <v>18820.143884892088</v>
+        <v>43088.23529411765</v>
       </c>
       <c r="O44" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P44" s="21"/>
+    </row>
+    <row r="45" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C45" s="4">
-        <v>11000000</v>
+        <v>2390000</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H45" s="2">
-        <v>406</v>
+        <v>200</v>
       </c>
       <c r="I45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N45" s="6">
         <f t="shared" si="1"/>
-        <v>27093.596059113301</v>
+        <v>11950</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P45" s="21"/>
+    </row>
+    <row r="46" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C46" s="4">
-        <v>3990000</v>
+        <v>13400000</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H46" s="2">
-        <v>924</v>
+        <v>894</v>
       </c>
       <c r="I46" s="2">
         <v>3</v>
       </c>
       <c r="J46" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" s="2">
         <v>6</v>
@@ -4503,49 +4653,50 @@
         <v>20</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N46" s="6">
         <f t="shared" si="1"/>
-        <v>4318.181818181818</v>
+        <v>14988.814317673377</v>
       </c>
       <c r="O46" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P46" s="21"/>
+    </row>
+    <row r="47" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C47" s="4">
-        <v>8790000</v>
+        <v>39450999</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>236</v>
+        <v>61</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>237</v>
+        <v>62</v>
       </c>
       <c r="H47" s="2">
-        <v>204</v>
+        <v>584</v>
       </c>
       <c r="I47" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J47" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K47" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>20</v>
@@ -4555,21 +4706,22 @@
       </c>
       <c r="N47" s="6">
         <f t="shared" si="1"/>
-        <v>43088.23529411765</v>
+        <v>67553.080479452052</v>
       </c>
       <c r="O47" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P47" s="21"/>
+    </row>
+    <row r="48" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C48" s="4">
-        <v>2390000</v>
+        <v>1500000</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>240</v>
@@ -4578,13 +4730,13 @@
         <v>25</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>47</v>
+        <v>241</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H48" s="2">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="I48" s="2">
         <v>2</v>
@@ -4593,55 +4745,56 @@
         <v>1</v>
       </c>
       <c r="K48" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N48" s="6">
         <f t="shared" si="1"/>
-        <v>11950</v>
+        <v>5725.1908396946565</v>
       </c>
       <c r="O48" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P48" s="21"/>
+    </row>
+    <row r="49" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C49" s="4">
-        <v>13400000</v>
+        <v>5590000</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>245</v>
+        <v>108</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>246</v>
       </c>
       <c r="H49" s="2">
-        <v>894</v>
+        <v>228</v>
       </c>
       <c r="I49" s="2">
         <v>3</v>
       </c>
       <c r="J49" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K49" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>20</v>
@@ -4651,45 +4804,46 @@
       </c>
       <c r="N49" s="6">
         <f t="shared" si="1"/>
-        <v>14988.814317673377</v>
+        <v>24517.543859649122</v>
       </c>
       <c r="O49" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P49" s="21"/>
+    </row>
+    <row r="50" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C50" s="4">
-        <v>39450999</v>
+        <v>5800000</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>249</v>
+        <v>97</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>66</v>
+        <v>249</v>
       </c>
       <c r="H50" s="2">
-        <v>584</v>
+        <v>234</v>
       </c>
       <c r="I50" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J50" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K50" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>20</v>
@@ -4699,21 +4853,22 @@
       </c>
       <c r="N50" s="6">
         <f t="shared" si="1"/>
-        <v>67553.080479452052</v>
+        <v>24786.324786324785</v>
       </c>
       <c r="O50" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P50" s="21"/>
+    </row>
+    <row r="51" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>251</v>
       </c>
       <c r="C51" s="4">
-        <v>1500000</v>
+        <v>5500000</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>252</v>
@@ -4728,55 +4883,56 @@
         <v>254</v>
       </c>
       <c r="H51" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I51" s="2">
+        <v>3</v>
+      </c>
+      <c r="J51" s="2">
         <v>2</v>
       </c>
-      <c r="J51" s="2">
-        <v>1</v>
-      </c>
       <c r="K51" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N51" s="6">
         <f t="shared" si="1"/>
-        <v>5725.1908396946565</v>
+        <v>21072.796934865899</v>
       </c>
       <c r="O51" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P51" s="21"/>
+    </row>
+    <row r="52" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C52" s="4">
-        <v>5590000</v>
+        <v>2700000</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H52" s="2">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="I52" s="2">
         <v>3</v>
@@ -4788,261 +4944,123 @@
         <v>2</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N52" s="6">
         <f t="shared" si="1"/>
-        <v>24517.543859649122</v>
+        <v>23478.260869565216</v>
       </c>
       <c r="O52" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P52" s="21"/>
+    </row>
+    <row r="53" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C53" s="4">
-        <v>5800000</v>
+        <v>3799900</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>105</v>
+        <v>263</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>261</v>
+        <v>57</v>
       </c>
       <c r="H53" s="2">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="I53" s="2">
         <v>3</v>
       </c>
       <c r="J53" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="2">
         <v>2</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N53" s="6">
         <f t="shared" si="1"/>
-        <v>24786.324786324785</v>
+        <v>24358.333333333332</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="P53" s="21"/>
+    </row>
+    <row r="54" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C54" s="4">
-        <v>5500000</v>
+        <v>1450000</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H54" s="2">
-        <v>261</v>
+        <v>140</v>
       </c>
       <c r="I54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2">
         <v>2</v>
       </c>
-      <c r="K54" s="2">
-        <v>4</v>
-      </c>
       <c r="L54" s="2" t="s">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N54" s="6">
         <f t="shared" si="1"/>
-        <v>21072.796934865899</v>
+        <v>10357.142857142857</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C55" s="4">
-        <v>2700000</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="H55" s="2">
-        <v>115</v>
-      </c>
-      <c r="I55" s="2">
-        <v>3</v>
-      </c>
-      <c r="J55" s="2">
-        <v>2</v>
-      </c>
-      <c r="K55" s="2">
-        <v>2</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="N55" s="6">
-        <f t="shared" si="1"/>
-        <v>23478.260869565216</v>
-      </c>
-      <c r="O55" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C56" s="4">
-        <v>3799900</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H56" s="2">
-        <v>156</v>
-      </c>
-      <c r="I56" s="2">
-        <v>3</v>
-      </c>
-      <c r="J56" s="2">
-        <v>3</v>
-      </c>
-      <c r="K56" s="2">
-        <v>2</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="N56" s="6">
-        <f t="shared" si="1"/>
-        <v>24358.333333333332</v>
-      </c>
-      <c r="O56" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C57" s="4">
-        <v>1450000</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="H57" s="2">
-        <v>140</v>
-      </c>
-      <c r="I57" s="2">
-        <v>2</v>
-      </c>
-      <c r="J57" s="2">
-        <v>1</v>
-      </c>
-      <c r="K57" s="2">
-        <v>2</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="N57" s="6">
-        <f t="shared" si="1"/>
-        <v>10357.142857142857</v>
-      </c>
-      <c r="O57" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="P54" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O57" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="P1:R1"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="O3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -5051,55 +5069,67 @@
     <hyperlink ref="O6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="O7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="O8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="O9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="O11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="O12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="O13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="O14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="O16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="O17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="O18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="O19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="O20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="O21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="O22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="O23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="O24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="O25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="O26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="O27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="O28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="O29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="O30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="O31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="O32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="O33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="O34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="O35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="O36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="O37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="O38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="O39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="O40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="O41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="O43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="O46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="O47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="O48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="O49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="O50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="O51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="O52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="O53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="O54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="O55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="O56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="O57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="R2" r:id="rId54" xr:uid="{BE8BA0D7-E1F5-4BAD-BEBF-3BB956A6A942}"/>
+    <hyperlink ref="Q2" r:id="rId55" xr:uid="{EDDEC89A-A96A-4068-8A16-E08FE0AD7B87}"/>
+    <hyperlink ref="P3" r:id="rId56" xr:uid="{020B422E-4D11-4170-ADEA-F371ABE3C095}"/>
+    <hyperlink ref="Q3" r:id="rId57" xr:uid="{DAB580CB-496B-4834-9908-E1BBEEE3D657}"/>
+    <hyperlink ref="R3" r:id="rId58" xr:uid="{79B1C097-55E9-4FF0-9EE6-1E42D21089AD}"/>
+    <hyperlink ref="P2" r:id="rId59" xr:uid="{3B0696F3-E2CC-4402-8221-B0A749D5CC63}"/>
+    <hyperlink ref="P4" r:id="rId60" xr:uid="{1BCD23A9-4AD8-4058-82A4-747C37833F05}"/>
+    <hyperlink ref="Q4" r:id="rId61" xr:uid="{EBFCBAAA-A85C-4090-8F61-39EC5B86D92F}"/>
+    <hyperlink ref="R4" r:id="rId62" xr:uid="{1AAF8534-F3CE-4B1A-9CA1-EE84649BA73B}"/>
+    <hyperlink ref="P5" r:id="rId63" xr:uid="{C9A1ACA8-C0C2-41E7-9177-51AC94CA6578}"/>
+    <hyperlink ref="Q5" r:id="rId64" xr:uid="{F8E70023-A9E9-4AE5-8480-D1965ED02200}"/>
+    <hyperlink ref="R5" r:id="rId65" xr:uid="{CD6E0E06-A475-438F-AB35-622F92EAEAE4}"/>
+    <hyperlink ref="P6" r:id="rId66" xr:uid="{C2BED095-D754-415E-A8FE-159356F3807A}"/>
+    <hyperlink ref="Q6" r:id="rId67" xr:uid="{9F389B3A-E365-4F68-A89E-88C363E0E83C}"/>
+    <hyperlink ref="R6" r:id="rId68" xr:uid="{4BACAE67-100C-4A4D-8409-BBBC17505BCB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -5108,7 +5138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE4EB3E-525F-4E65-805F-3AFBA5ACC095}">
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -5124,2505 +5154,2467 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-    </row>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="L4" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-    </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    </row>
+    <row r="5" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C5" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F5" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="L5" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="H4" s="11" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="C6" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="F6" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="H6" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="I6" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="13" t="s">
+    </row>
+    <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D7" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F7" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K5" s="16" t="s">
+    </row>
+    <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="B8" s="10" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="C8" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="J9" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="F10" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="I11" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L6" s="17" t="s">
+      <c r="B12" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K7" s="16" t="s">
+      <c r="J14" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L7" s="17" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="B15" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="K8" s="16" t="s">
+      <c r="I15" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L8" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="B16" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="H16" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="I16" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="K9" s="16" t="s">
+    </row>
+    <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L9" s="17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="B18" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K10" s="16" t="s">
+      <c r="I18" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L10" s="17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K11" s="16" t="s">
+      <c r="B19" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L11" s="17" t="s">
+      <c r="B20" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="K12" s="16" t="s">
+    <row r="21" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L12" s="17" t="s">
+      <c r="B21" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L23" s="15" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K13" s="16" t="s">
+    <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L13" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K14" s="16" t="s">
+      <c r="B24" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L14" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K15" s="16" t="s">
+      <c r="B25" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L15" s="17" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K16" s="16" t="s">
+      <c r="B26" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L16" s="17" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K17" s="16" t="s">
+      <c r="B27" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L17" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K18" s="16" t="s">
+      <c r="B28" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L18" s="17" t="s">
+      <c r="B29" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L29" s="15" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K19" s="16" t="s">
+    <row r="30" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L19" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K20" s="16" t="s">
+      <c r="B30" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L20" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K21" s="16" t="s">
+      <c r="B31" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="L21" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I22" s="13" t="s">
+      <c r="B32" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L51" s="15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L52" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="J22" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L23" s="17" t="s">
+    </row>
+    <row r="53" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L53" s="15" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L54" s="15" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L56" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L57" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L58" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L59" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L60" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L61" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L62" s="15" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="E24" s="13" t="s">
+    <row r="63" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L63" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J64" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E25" s="13" t="s">
+      <c r="K64" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L64" s="15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J65" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L25" s="17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="K65" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L65" s="15" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="J66" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L26" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L27" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>417</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L28" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L29" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L30" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L32" s="17" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K33" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L34" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L36" s="17" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K37" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L38" s="17" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K39" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L39" s="17" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K40" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L40" s="17" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>468</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>469</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>473</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="K42" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L42" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K43" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L43" s="17" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L44" s="17" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J45" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K45" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L45" s="17" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K46" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L46" s="17" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K47" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L47" s="17" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>504</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K48" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L48" s="17" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="F49" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J49" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K49" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L49" s="17" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K50" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L50" s="17" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>517</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K51" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L51" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>519</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K52" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L52" s="17" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>520</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K53" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L53" s="17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="H54" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J54" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K54" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L54" s="17" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>527</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="H55" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="K55" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L55" s="17" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="F56" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G56" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H56" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J56" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="K56" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L56" s="17" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>536</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H57" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="K57" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L57" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>539</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F58" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>542</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K58" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L58" s="17" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>543</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>544</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>545</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J59" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K59" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L59" s="17" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>547</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F60" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>548</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J60" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K60" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L60" s="17" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>549</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>550</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>551</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I61" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J61" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K61" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L61" s="17" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>552</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J62" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K62" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L62" s="17" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>556</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E63" s="13" t="s">
+      <c r="K66" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L66" s="15" t="s">
         <v>558</v>
       </c>
-      <c r="F63" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G63" s="13" t="s">
+    </row>
+    <row r="67" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="H63" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I63" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J63" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K63" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L63" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>556</v>
-      </c>
-      <c r="C64" s="13" t="s">
+      <c r="B67" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="D64" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G64" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="J64" s="13" t="s">
+      <c r="C67" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="K64" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L64" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B65" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="E67" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="F67" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G67" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="E65" s="13" t="s">
+      <c r="H67" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="L67" s="15" t="s">
         <v>565</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I65" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K65" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L65" s="17" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="F66" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="I66" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J66" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K66" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L66" s="17" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="I67" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="J67" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="K67" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L67" s="17" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>575</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>576</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>577</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>578</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>579</v>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="G68" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="H68" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="I68" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J68" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="K68" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L68" s="17" t="s">
-        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -7649,120 +7641,118 @@
     <hyperlink ref="L12" r:id="rId16" xr:uid="{30CF42F7-A461-4838-B669-86662996EF17}"/>
     <hyperlink ref="K13" r:id="rId17" xr:uid="{7730DBD3-1802-4463-85B0-0502C8C7F04E}"/>
     <hyperlink ref="L13" r:id="rId18" xr:uid="{B6AC35DB-CE54-486C-822F-88A9615997F9}"/>
-    <hyperlink ref="K14" r:id="rId19" xr:uid="{B830F598-FC60-4289-9C28-95626B4DFFB8}"/>
-    <hyperlink ref="L14" r:id="rId20" xr:uid="{7D9333C5-7752-4147-A175-9A7081A537C6}"/>
-    <hyperlink ref="K15" r:id="rId21" xr:uid="{3FEB4CE7-8B88-4F56-AC2D-5CB6AECC028E}"/>
-    <hyperlink ref="L15" r:id="rId22" xr:uid="{6DE7D873-3B9C-4525-8859-F61F601368C9}"/>
-    <hyperlink ref="K16" r:id="rId23" xr:uid="{43836271-9413-4360-BC65-34EC88B11749}"/>
-    <hyperlink ref="L16" r:id="rId24" xr:uid="{C5B1CA09-C6E2-4EC6-9E25-25AB494CF24E}"/>
-    <hyperlink ref="K17" r:id="rId25" xr:uid="{7FC98C2B-ED5E-47E2-B93A-E3155D9F6B81}"/>
-    <hyperlink ref="L17" r:id="rId26" xr:uid="{845FED0C-1C84-41B6-83E2-FC826944D0BD}"/>
-    <hyperlink ref="K18" r:id="rId27" xr:uid="{DD4EF9BB-52F6-40B9-9B1E-70979B638B20}"/>
-    <hyperlink ref="L18" r:id="rId28" xr:uid="{03E382F7-9172-4F08-9E38-B7750C2C6912}"/>
-    <hyperlink ref="K19" r:id="rId29" xr:uid="{9EEDEF39-1629-4B9E-ABB1-7F12AB7F3A89}"/>
-    <hyperlink ref="L19" r:id="rId30" xr:uid="{C8E65280-E910-474F-BC91-A5C0131D7867}"/>
-    <hyperlink ref="K20" r:id="rId31" xr:uid="{3ACC80F2-F5E0-408D-B686-770F664506BE}"/>
-    <hyperlink ref="L20" r:id="rId32" xr:uid="{8B9D0C4B-ADA1-4991-8D1C-3D446CFE1FE5}"/>
-    <hyperlink ref="K21" r:id="rId33" xr:uid="{EA1CB156-8D6C-46B4-A9BB-8042F588BFD4}"/>
-    <hyperlink ref="L21" r:id="rId34" xr:uid="{30FDA3FB-D9DB-453F-82E6-CE15FF8B2DB1}"/>
-    <hyperlink ref="K22" r:id="rId35" xr:uid="{F1FB4314-AD13-4B3F-AC37-B94AE57D8474}"/>
-    <hyperlink ref="L22" r:id="rId36" xr:uid="{B7EB7E3A-C7FD-4B9D-AC06-5E4C4DABFDD2}"/>
-    <hyperlink ref="K23" r:id="rId37" xr:uid="{7E1064C4-6193-47CD-A209-F640179EA027}"/>
-    <hyperlink ref="L23" r:id="rId38" xr:uid="{0B4C373A-97F5-4887-86BD-479AD623264E}"/>
-    <hyperlink ref="K24" r:id="rId39" xr:uid="{DF5CB5E2-CE9A-40E7-972C-CCD668667AA7}"/>
-    <hyperlink ref="L24" r:id="rId40" xr:uid="{12010895-5F75-4375-B859-818261DE8B35}"/>
-    <hyperlink ref="K25" r:id="rId41" xr:uid="{6C611473-D760-4B86-BEBE-794BA6D56F41}"/>
-    <hyperlink ref="L25" r:id="rId42" xr:uid="{853589D3-1905-403A-BA1B-A61612C0DB97}"/>
-    <hyperlink ref="K26" r:id="rId43" xr:uid="{35B75D9F-C637-4AC3-A0E7-4484044C256E}"/>
-    <hyperlink ref="L26" r:id="rId44" xr:uid="{64B20EE0-8975-4CF3-A3B6-945AB18B96D1}"/>
-    <hyperlink ref="K27" r:id="rId45" xr:uid="{672DB57C-DA9E-44B0-A4BB-D62E3553F9A2}"/>
-    <hyperlink ref="L27" r:id="rId46" xr:uid="{AE06C2E3-DD52-4EDC-BD3B-250973FD8C8B}"/>
-    <hyperlink ref="K28" r:id="rId47" xr:uid="{345849FC-C32C-4B0B-8C02-93CCD487C3FF}"/>
-    <hyperlink ref="L28" r:id="rId48" xr:uid="{74E34758-C575-44DD-A04F-094D01E01DF0}"/>
-    <hyperlink ref="K29" r:id="rId49" xr:uid="{B364DEB5-38E0-41C6-A9D8-9EF5324EE0C2}"/>
-    <hyperlink ref="L29" r:id="rId50" xr:uid="{2E84E887-78BF-4F91-BF68-2FF307A0B11F}"/>
-    <hyperlink ref="K30" r:id="rId51" xr:uid="{E7F2E7C1-E28D-4F6F-B319-7FFD45CC8564}"/>
-    <hyperlink ref="L30" r:id="rId52" xr:uid="{8290AF6E-6161-41D2-BDBC-65B0DED551D9}"/>
-    <hyperlink ref="K31" r:id="rId53" xr:uid="{CB5CDB79-EF82-4717-B8B6-85A08BCEECA1}"/>
-    <hyperlink ref="L31" r:id="rId54" xr:uid="{FF0EA9BA-7129-4149-AD68-02196F1FCF2E}"/>
-    <hyperlink ref="K32" r:id="rId55" xr:uid="{09C09C03-0DC3-453D-9B25-B96A914794D4}"/>
-    <hyperlink ref="L32" r:id="rId56" xr:uid="{A2038ED2-95A2-4788-82C3-8E593F60C22D}"/>
-    <hyperlink ref="K33" r:id="rId57" xr:uid="{4CDE133D-883F-4170-805C-DAE94A310418}"/>
-    <hyperlink ref="L33" r:id="rId58" xr:uid="{878584F4-2BB5-425F-882E-851E0DC02E4E}"/>
-    <hyperlink ref="K34" r:id="rId59" xr:uid="{40315579-6159-4D4C-95FE-80658D93AC59}"/>
-    <hyperlink ref="L34" r:id="rId60" xr:uid="{6219AB8B-A700-42D6-B978-F07567E7CFDD}"/>
-    <hyperlink ref="K35" r:id="rId61" xr:uid="{F8660384-44D4-489B-B52A-60F913D0B8B1}"/>
-    <hyperlink ref="L35" r:id="rId62" xr:uid="{3FEB7099-B508-4E0F-9853-DC635F72D5CE}"/>
-    <hyperlink ref="K36" r:id="rId63" xr:uid="{22CBCB62-BFCC-4437-8A28-502BD4386EF8}"/>
-    <hyperlink ref="L36" r:id="rId64" xr:uid="{A034E180-9DF5-45A5-BCFC-9CB38FF1D685}"/>
-    <hyperlink ref="K37" r:id="rId65" xr:uid="{E0B5DB15-0D45-458A-8728-10402C834DA7}"/>
-    <hyperlink ref="L37" r:id="rId66" xr:uid="{4B74F348-2F31-41C9-BA1F-B4644D010732}"/>
-    <hyperlink ref="K38" r:id="rId67" xr:uid="{3D60FE8B-BB1F-4BB8-A5DC-B944826C5EBB}"/>
-    <hyperlink ref="L38" r:id="rId68" xr:uid="{ED579882-7CE0-4614-AC66-EA222C9D9C2C}"/>
-    <hyperlink ref="K39" r:id="rId69" xr:uid="{271405A8-39CE-48C8-B5E9-461B72BA4808}"/>
-    <hyperlink ref="L39" r:id="rId70" xr:uid="{D5FD901E-009A-47E9-B13C-22FC1651138C}"/>
-    <hyperlink ref="K40" r:id="rId71" xr:uid="{BD964EB2-6F62-4CEC-8402-AD29C11E3AD7}"/>
-    <hyperlink ref="L40" r:id="rId72" xr:uid="{F81EA263-B932-4E12-97A1-7AB3C47C2B84}"/>
-    <hyperlink ref="K41" r:id="rId73" xr:uid="{372040BD-7B82-45FA-8172-4167C01DBBB8}"/>
-    <hyperlink ref="L41" r:id="rId74" xr:uid="{9D3E56EE-6A68-4630-B821-11524AACADD7}"/>
-    <hyperlink ref="K42" r:id="rId75" xr:uid="{99148B58-5C18-4470-8C13-D90BB31E02A7}"/>
-    <hyperlink ref="L42" r:id="rId76" xr:uid="{3D5F25EF-1F58-4783-B201-8EFBF18EB1B0}"/>
-    <hyperlink ref="K43" r:id="rId77" xr:uid="{DCD22E7A-AA2B-4485-A691-7976E16A0D85}"/>
-    <hyperlink ref="L43" r:id="rId78" xr:uid="{1EE2349D-9C2E-4749-8A09-AA21FE55FBF6}"/>
-    <hyperlink ref="K44" r:id="rId79" xr:uid="{40C2C550-D51E-4D32-AC5D-5F0C0C687B72}"/>
-    <hyperlink ref="L44" r:id="rId80" xr:uid="{CDC28CBD-0E42-474E-B44B-BF483ED67DC2}"/>
-    <hyperlink ref="K45" r:id="rId81" xr:uid="{C8BE41D9-90ED-48D5-9996-8483B227AE7E}"/>
-    <hyperlink ref="L45" r:id="rId82" xr:uid="{64CB9C6D-2578-4821-A503-80F7FC271F39}"/>
-    <hyperlink ref="K46" r:id="rId83" xr:uid="{6B37EC80-F830-4420-B6C7-9CFD5B6CC057}"/>
-    <hyperlink ref="L46" r:id="rId84" xr:uid="{69FDDAC4-DC92-4911-B6F4-8E3C0311E87F}"/>
-    <hyperlink ref="K47" r:id="rId85" xr:uid="{7EA93714-217A-482D-A0ED-E99753996D2B}"/>
-    <hyperlink ref="L47" r:id="rId86" xr:uid="{F3EB129C-7BEF-4800-9781-FBB881C8527E}"/>
-    <hyperlink ref="K48" r:id="rId87" xr:uid="{955B672A-E00B-4E47-A454-ACD2F78C5A35}"/>
-    <hyperlink ref="L48" r:id="rId88" xr:uid="{AA7E1EEF-1CD5-4EF5-B4AF-B0FF91086F84}"/>
-    <hyperlink ref="K49" r:id="rId89" xr:uid="{C6FFEFA9-0322-4D72-885C-CF000388C6D2}"/>
-    <hyperlink ref="L49" r:id="rId90" xr:uid="{5E9E6D9D-5572-4F21-9F3D-5AD709776259}"/>
-    <hyperlink ref="K50" r:id="rId91" xr:uid="{4101324D-51C5-4E08-A308-650F529AB0B3}"/>
-    <hyperlink ref="L50" r:id="rId92" xr:uid="{BB12D16A-288A-4E8D-AE62-0790E3B7B821}"/>
-    <hyperlink ref="K51" r:id="rId93" xr:uid="{9ACBC60A-5287-47D1-95C9-029D500EF084}"/>
-    <hyperlink ref="L51" r:id="rId94" xr:uid="{7AAAD290-CE85-4C53-A136-9548294613F2}"/>
-    <hyperlink ref="K52" r:id="rId95" xr:uid="{01614361-6B56-43AF-8E22-A16B9512D78C}"/>
-    <hyperlink ref="L52" r:id="rId96" xr:uid="{646E454E-C442-4240-998E-53AA037EF6A4}"/>
-    <hyperlink ref="K53" r:id="rId97" xr:uid="{4EFD79B1-73D1-4BA6-A187-3D29E3EB7E50}"/>
-    <hyperlink ref="L53" r:id="rId98" xr:uid="{5D013632-5DB4-4B3F-BCAF-ADFD623AADD1}"/>
-    <hyperlink ref="K54" r:id="rId99" xr:uid="{20913375-4560-43A6-B330-2DCC5B306D32}"/>
-    <hyperlink ref="L54" r:id="rId100" xr:uid="{05E565C8-0A4D-4C71-AA30-4DA1D3CCEDE4}"/>
-    <hyperlink ref="K55" r:id="rId101" xr:uid="{3816F88D-8A46-4452-9EEB-A77EE2551451}"/>
-    <hyperlink ref="L55" r:id="rId102" xr:uid="{438F7334-F146-4317-9B59-2317E92AFCCA}"/>
-    <hyperlink ref="K56" r:id="rId103" xr:uid="{04FC723B-E18A-4351-8AB2-7DD3B1AD99A6}"/>
-    <hyperlink ref="L56" r:id="rId104" xr:uid="{5A8A2328-8FB8-49E8-838A-4E34E42C8E65}"/>
-    <hyperlink ref="K57" r:id="rId105" xr:uid="{6F504530-685F-44D7-B8B0-98B87A2CF79B}"/>
-    <hyperlink ref="L57" r:id="rId106" xr:uid="{16283459-BF89-4C12-83CF-1A85A56AABF8}"/>
-    <hyperlink ref="K58" r:id="rId107" xr:uid="{6361F3C6-A23B-4A21-8824-16E6A63C536B}"/>
-    <hyperlink ref="L58" r:id="rId108" xr:uid="{A4122003-D4EB-4517-B2FA-2B1FEB7B42DD}"/>
-    <hyperlink ref="K59" r:id="rId109" xr:uid="{94B6AE6C-607C-4321-8CB2-4BC557FAD082}"/>
-    <hyperlink ref="L59" r:id="rId110" xr:uid="{F57B9BAB-105B-4373-BCAC-952D44747339}"/>
-    <hyperlink ref="K60" r:id="rId111" xr:uid="{ABDF0A62-737B-4E2A-B63E-3765C7A4E99F}"/>
-    <hyperlink ref="L60" r:id="rId112" xr:uid="{D8FAD234-872D-447F-A9F1-9704C5F6F724}"/>
-    <hyperlink ref="K61" r:id="rId113" xr:uid="{AC9C70B0-F8DD-406B-A408-A50C40B0AC82}"/>
-    <hyperlink ref="L61" r:id="rId114" xr:uid="{DDCE89F6-6E3B-4F0B-AB3F-1430EC489668}"/>
-    <hyperlink ref="K62" r:id="rId115" xr:uid="{00A98085-AC6C-45CB-AF2C-29E690271118}"/>
-    <hyperlink ref="L62" r:id="rId116" xr:uid="{1EC2ECBD-FC8D-4C02-BED0-30EC56074154}"/>
-    <hyperlink ref="K63" r:id="rId117" xr:uid="{93A6E351-E347-4C9F-BAEB-543CCF70E540}"/>
-    <hyperlink ref="L63" r:id="rId118" xr:uid="{F1D72214-5A19-4A02-84A7-3D1BE636EC23}"/>
-    <hyperlink ref="K64" r:id="rId119" xr:uid="{A3182BBA-20AD-4989-A0B1-38689FBADC2C}"/>
-    <hyperlink ref="L64" r:id="rId120" xr:uid="{AEF98270-4050-4DF1-B008-58C6D73AE3FF}"/>
-    <hyperlink ref="K65" r:id="rId121" xr:uid="{03F81F9F-2569-406B-8273-9ED34FFA134F}"/>
-    <hyperlink ref="L65" r:id="rId122" xr:uid="{4D84AFCF-A4E5-42EE-B8BB-8611288907DA}"/>
-    <hyperlink ref="K66" r:id="rId123" xr:uid="{86224AF8-C32F-485F-815E-3A78BB586CA1}"/>
-    <hyperlink ref="L66" r:id="rId124" xr:uid="{EEAE2B05-CBB2-4C7B-BC1A-846467A81F41}"/>
-    <hyperlink ref="K67" r:id="rId125" xr:uid="{73FBBCCE-0DD9-47A7-B5B4-BC6E020F06E5}"/>
-    <hyperlink ref="L67" r:id="rId126" xr:uid="{07713F10-1C46-4157-98CD-C35C719EDF0D}"/>
-    <hyperlink ref="K68" r:id="rId127" xr:uid="{F3C65C69-3A13-4454-B766-F13E8928587B}"/>
-    <hyperlink ref="L68" r:id="rId128" xr:uid="{3439DC43-D106-4F9B-9C7D-6A6F366CBC3C}"/>
+    <hyperlink ref="K14" r:id="rId19" xr:uid="{3FEB4CE7-8B88-4F56-AC2D-5CB6AECC028E}"/>
+    <hyperlink ref="L14" r:id="rId20" xr:uid="{6DE7D873-3B9C-4525-8859-F61F601368C9}"/>
+    <hyperlink ref="K15" r:id="rId21" xr:uid="{43836271-9413-4360-BC65-34EC88B11749}"/>
+    <hyperlink ref="L15" r:id="rId22" xr:uid="{C5B1CA09-C6E2-4EC6-9E25-25AB494CF24E}"/>
+    <hyperlink ref="K16" r:id="rId23" xr:uid="{7FC98C2B-ED5E-47E2-B93A-E3155D9F6B81}"/>
+    <hyperlink ref="L16" r:id="rId24" xr:uid="{845FED0C-1C84-41B6-83E2-FC826944D0BD}"/>
+    <hyperlink ref="K17" r:id="rId25" xr:uid="{DD4EF9BB-52F6-40B9-9B1E-70979B638B20}"/>
+    <hyperlink ref="L17" r:id="rId26" xr:uid="{03E382F7-9172-4F08-9E38-B7750C2C6912}"/>
+    <hyperlink ref="K18" r:id="rId27" xr:uid="{9EEDEF39-1629-4B9E-ABB1-7F12AB7F3A89}"/>
+    <hyperlink ref="L18" r:id="rId28" xr:uid="{C8E65280-E910-474F-BC91-A5C0131D7867}"/>
+    <hyperlink ref="K19" r:id="rId29" xr:uid="{3ACC80F2-F5E0-408D-B686-770F664506BE}"/>
+    <hyperlink ref="L19" r:id="rId30" xr:uid="{8B9D0C4B-ADA1-4991-8D1C-3D446CFE1FE5}"/>
+    <hyperlink ref="K20" r:id="rId31" xr:uid="{EA1CB156-8D6C-46B4-A9BB-8042F588BFD4}"/>
+    <hyperlink ref="L20" r:id="rId32" xr:uid="{30FDA3FB-D9DB-453F-82E6-CE15FF8B2DB1}"/>
+    <hyperlink ref="K21" r:id="rId33" xr:uid="{F1FB4314-AD13-4B3F-AC37-B94AE57D8474}"/>
+    <hyperlink ref="L21" r:id="rId34" xr:uid="{B7EB7E3A-C7FD-4B9D-AC06-5E4C4DABFDD2}"/>
+    <hyperlink ref="K22" r:id="rId35" xr:uid="{7E1064C4-6193-47CD-A209-F640179EA027}"/>
+    <hyperlink ref="L22" r:id="rId36" xr:uid="{0B4C373A-97F5-4887-86BD-479AD623264E}"/>
+    <hyperlink ref="K23" r:id="rId37" xr:uid="{DF5CB5E2-CE9A-40E7-972C-CCD668667AA7}"/>
+    <hyperlink ref="L23" r:id="rId38" xr:uid="{12010895-5F75-4375-B859-818261DE8B35}"/>
+    <hyperlink ref="K24" r:id="rId39" xr:uid="{6C611473-D760-4B86-BEBE-794BA6D56F41}"/>
+    <hyperlink ref="L24" r:id="rId40" xr:uid="{853589D3-1905-403A-BA1B-A61612C0DB97}"/>
+    <hyperlink ref="K25" r:id="rId41" xr:uid="{35B75D9F-C637-4AC3-A0E7-4484044C256E}"/>
+    <hyperlink ref="L25" r:id="rId42" xr:uid="{64B20EE0-8975-4CF3-A3B6-945AB18B96D1}"/>
+    <hyperlink ref="K26" r:id="rId43" xr:uid="{672DB57C-DA9E-44B0-A4BB-D62E3553F9A2}"/>
+    <hyperlink ref="L26" r:id="rId44" xr:uid="{AE06C2E3-DD52-4EDC-BD3B-250973FD8C8B}"/>
+    <hyperlink ref="K27" r:id="rId45" xr:uid="{345849FC-C32C-4B0B-8C02-93CCD487C3FF}"/>
+    <hyperlink ref="L27" r:id="rId46" xr:uid="{74E34758-C575-44DD-A04F-094D01E01DF0}"/>
+    <hyperlink ref="K28" r:id="rId47" xr:uid="{B364DEB5-38E0-41C6-A9D8-9EF5324EE0C2}"/>
+    <hyperlink ref="L28" r:id="rId48" xr:uid="{2E84E887-78BF-4F91-BF68-2FF307A0B11F}"/>
+    <hyperlink ref="K29" r:id="rId49" xr:uid="{E7F2E7C1-E28D-4F6F-B319-7FFD45CC8564}"/>
+    <hyperlink ref="L29" r:id="rId50" xr:uid="{8290AF6E-6161-41D2-BDBC-65B0DED551D9}"/>
+    <hyperlink ref="K30" r:id="rId51" xr:uid="{CB5CDB79-EF82-4717-B8B6-85A08BCEECA1}"/>
+    <hyperlink ref="L30" r:id="rId52" xr:uid="{FF0EA9BA-7129-4149-AD68-02196F1FCF2E}"/>
+    <hyperlink ref="K31" r:id="rId53" xr:uid="{09C09C03-0DC3-453D-9B25-B96A914794D4}"/>
+    <hyperlink ref="L31" r:id="rId54" xr:uid="{A2038ED2-95A2-4788-82C3-8E593F60C22D}"/>
+    <hyperlink ref="K32" r:id="rId55" xr:uid="{4CDE133D-883F-4170-805C-DAE94A310418}"/>
+    <hyperlink ref="L32" r:id="rId56" xr:uid="{878584F4-2BB5-425F-882E-851E0DC02E4E}"/>
+    <hyperlink ref="K33" r:id="rId57" xr:uid="{40315579-6159-4D4C-95FE-80658D93AC59}"/>
+    <hyperlink ref="L33" r:id="rId58" xr:uid="{6219AB8B-A700-42D6-B978-F07567E7CFDD}"/>
+    <hyperlink ref="K34" r:id="rId59" xr:uid="{F8660384-44D4-489B-B52A-60F913D0B8B1}"/>
+    <hyperlink ref="L34" r:id="rId60" xr:uid="{3FEB7099-B508-4E0F-9853-DC635F72D5CE}"/>
+    <hyperlink ref="K35" r:id="rId61" xr:uid="{22CBCB62-BFCC-4437-8A28-502BD4386EF8}"/>
+    <hyperlink ref="L35" r:id="rId62" xr:uid="{A034E180-9DF5-45A5-BCFC-9CB38FF1D685}"/>
+    <hyperlink ref="K36" r:id="rId63" xr:uid="{E0B5DB15-0D45-458A-8728-10402C834DA7}"/>
+    <hyperlink ref="L36" r:id="rId64" xr:uid="{4B74F348-2F31-41C9-BA1F-B4644D010732}"/>
+    <hyperlink ref="K37" r:id="rId65" xr:uid="{3D60FE8B-BB1F-4BB8-A5DC-B944826C5EBB}"/>
+    <hyperlink ref="L37" r:id="rId66" xr:uid="{ED579882-7CE0-4614-AC66-EA222C9D9C2C}"/>
+    <hyperlink ref="K38" r:id="rId67" xr:uid="{271405A8-39CE-48C8-B5E9-461B72BA4808}"/>
+    <hyperlink ref="L38" r:id="rId68" xr:uid="{D5FD901E-009A-47E9-B13C-22FC1651138C}"/>
+    <hyperlink ref="K39" r:id="rId69" xr:uid="{BD964EB2-6F62-4CEC-8402-AD29C11E3AD7}"/>
+    <hyperlink ref="L39" r:id="rId70" xr:uid="{F81EA263-B932-4E12-97A1-7AB3C47C2B84}"/>
+    <hyperlink ref="K40" r:id="rId71" xr:uid="{372040BD-7B82-45FA-8172-4167C01DBBB8}"/>
+    <hyperlink ref="L40" r:id="rId72" xr:uid="{9D3E56EE-6A68-4630-B821-11524AACADD7}"/>
+    <hyperlink ref="K41" r:id="rId73" xr:uid="{99148B58-5C18-4470-8C13-D90BB31E02A7}"/>
+    <hyperlink ref="L41" r:id="rId74" xr:uid="{3D5F25EF-1F58-4783-B201-8EFBF18EB1B0}"/>
+    <hyperlink ref="K42" r:id="rId75" xr:uid="{DCD22E7A-AA2B-4485-A691-7976E16A0D85}"/>
+    <hyperlink ref="L42" r:id="rId76" xr:uid="{1EE2349D-9C2E-4749-8A09-AA21FE55FBF6}"/>
+    <hyperlink ref="K43" r:id="rId77" xr:uid="{40C2C550-D51E-4D32-AC5D-5F0C0C687B72}"/>
+    <hyperlink ref="L43" r:id="rId78" xr:uid="{CDC28CBD-0E42-474E-B44B-BF483ED67DC2}"/>
+    <hyperlink ref="K44" r:id="rId79" xr:uid="{C8BE41D9-90ED-48D5-9996-8483B227AE7E}"/>
+    <hyperlink ref="L44" r:id="rId80" xr:uid="{64CB9C6D-2578-4821-A503-80F7FC271F39}"/>
+    <hyperlink ref="K45" r:id="rId81" xr:uid="{6B37EC80-F830-4420-B6C7-9CFD5B6CC057}"/>
+    <hyperlink ref="L45" r:id="rId82" xr:uid="{69FDDAC4-DC92-4911-B6F4-8E3C0311E87F}"/>
+    <hyperlink ref="K46" r:id="rId83" xr:uid="{7EA93714-217A-482D-A0ED-E99753996D2B}"/>
+    <hyperlink ref="L46" r:id="rId84" xr:uid="{F3EB129C-7BEF-4800-9781-FBB881C8527E}"/>
+    <hyperlink ref="K47" r:id="rId85" xr:uid="{955B672A-E00B-4E47-A454-ACD2F78C5A35}"/>
+    <hyperlink ref="L47" r:id="rId86" xr:uid="{AA7E1EEF-1CD5-4EF5-B4AF-B0FF91086F84}"/>
+    <hyperlink ref="K48" r:id="rId87" xr:uid="{C6FFEFA9-0322-4D72-885C-CF000388C6D2}"/>
+    <hyperlink ref="L48" r:id="rId88" xr:uid="{5E9E6D9D-5572-4F21-9F3D-5AD709776259}"/>
+    <hyperlink ref="K49" r:id="rId89" xr:uid="{4101324D-51C5-4E08-A308-650F529AB0B3}"/>
+    <hyperlink ref="L49" r:id="rId90" xr:uid="{BB12D16A-288A-4E8D-AE62-0790E3B7B821}"/>
+    <hyperlink ref="K50" r:id="rId91" xr:uid="{9ACBC60A-5287-47D1-95C9-029D500EF084}"/>
+    <hyperlink ref="L50" r:id="rId92" xr:uid="{7AAAD290-CE85-4C53-A136-9548294613F2}"/>
+    <hyperlink ref="K51" r:id="rId93" xr:uid="{01614361-6B56-43AF-8E22-A16B9512D78C}"/>
+    <hyperlink ref="L51" r:id="rId94" xr:uid="{646E454E-C442-4240-998E-53AA037EF6A4}"/>
+    <hyperlink ref="K52" r:id="rId95" xr:uid="{4EFD79B1-73D1-4BA6-A187-3D29E3EB7E50}"/>
+    <hyperlink ref="L52" r:id="rId96" xr:uid="{5D013632-5DB4-4B3F-BCAF-ADFD623AADD1}"/>
+    <hyperlink ref="K53" r:id="rId97" xr:uid="{20913375-4560-43A6-B330-2DCC5B306D32}"/>
+    <hyperlink ref="L53" r:id="rId98" xr:uid="{05E565C8-0A4D-4C71-AA30-4DA1D3CCEDE4}"/>
+    <hyperlink ref="K54" r:id="rId99" xr:uid="{3816F88D-8A46-4452-9EEB-A77EE2551451}"/>
+    <hyperlink ref="L54" r:id="rId100" xr:uid="{438F7334-F146-4317-9B59-2317E92AFCCA}"/>
+    <hyperlink ref="K55" r:id="rId101" xr:uid="{04FC723B-E18A-4351-8AB2-7DD3B1AD99A6}"/>
+    <hyperlink ref="L55" r:id="rId102" xr:uid="{5A8A2328-8FB8-49E8-838A-4E34E42C8E65}"/>
+    <hyperlink ref="K56" r:id="rId103" xr:uid="{6F504530-685F-44D7-B8B0-98B87A2CF79B}"/>
+    <hyperlink ref="L56" r:id="rId104" xr:uid="{16283459-BF89-4C12-83CF-1A85A56AABF8}"/>
+    <hyperlink ref="K57" r:id="rId105" xr:uid="{6361F3C6-A23B-4A21-8824-16E6A63C536B}"/>
+    <hyperlink ref="L57" r:id="rId106" xr:uid="{A4122003-D4EB-4517-B2FA-2B1FEB7B42DD}"/>
+    <hyperlink ref="K58" r:id="rId107" xr:uid="{94B6AE6C-607C-4321-8CB2-4BC557FAD082}"/>
+    <hyperlink ref="L58" r:id="rId108" xr:uid="{F57B9BAB-105B-4373-BCAC-952D44747339}"/>
+    <hyperlink ref="K59" r:id="rId109" xr:uid="{ABDF0A62-737B-4E2A-B63E-3765C7A4E99F}"/>
+    <hyperlink ref="L59" r:id="rId110" xr:uid="{D8FAD234-872D-447F-A9F1-9704C5F6F724}"/>
+    <hyperlink ref="K60" r:id="rId111" xr:uid="{AC9C70B0-F8DD-406B-A408-A50C40B0AC82}"/>
+    <hyperlink ref="L60" r:id="rId112" xr:uid="{DDCE89F6-6E3B-4F0B-AB3F-1430EC489668}"/>
+    <hyperlink ref="K61" r:id="rId113" xr:uid="{00A98085-AC6C-45CB-AF2C-29E690271118}"/>
+    <hyperlink ref="L61" r:id="rId114" xr:uid="{1EC2ECBD-FC8D-4C02-BED0-30EC56074154}"/>
+    <hyperlink ref="K62" r:id="rId115" xr:uid="{93A6E351-E347-4C9F-BAEB-543CCF70E540}"/>
+    <hyperlink ref="L62" r:id="rId116" xr:uid="{F1D72214-5A19-4A02-84A7-3D1BE636EC23}"/>
+    <hyperlink ref="K63" r:id="rId117" xr:uid="{A3182BBA-20AD-4989-A0B1-38689FBADC2C}"/>
+    <hyperlink ref="L63" r:id="rId118" xr:uid="{AEF98270-4050-4DF1-B008-58C6D73AE3FF}"/>
+    <hyperlink ref="K64" r:id="rId119" xr:uid="{03F81F9F-2569-406B-8273-9ED34FFA134F}"/>
+    <hyperlink ref="L64" r:id="rId120" xr:uid="{4D84AFCF-A4E5-42EE-B8BB-8611288907DA}"/>
+    <hyperlink ref="K65" r:id="rId121" xr:uid="{86224AF8-C32F-485F-815E-3A78BB586CA1}"/>
+    <hyperlink ref="L65" r:id="rId122" xr:uid="{EEAE2B05-CBB2-4C7B-BC1A-846467A81F41}"/>
+    <hyperlink ref="K66" r:id="rId123" xr:uid="{73FBBCCE-0DD9-47A7-B5B4-BC6E020F06E5}"/>
+    <hyperlink ref="L66" r:id="rId124" xr:uid="{07713F10-1C46-4157-98CD-C35C719EDF0D}"/>
+    <hyperlink ref="K67" r:id="rId125" xr:uid="{F3C65C69-3A13-4454-B766-F13E8928587B}"/>
+    <hyperlink ref="L67" r:id="rId126" xr:uid="{3439DC43-D106-4F9B-9C7D-6A6F366CBC3C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId129"/>
+    <tablePart r:id="rId127"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/propiedades.xlsx
+++ b/data/propiedades.xlsx
@@ -753,7 +753,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P2" s="19" t="n"/>
+      <c r="P2" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/48/92/61/90/1200x1200/1587104686.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="25.5" customHeight="1" s="9">
       <c r="A3" s="2" t="n">
@@ -814,7 +818,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P3" s="19" t="n"/>
+      <c r="P3" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/10/76/67/1200x1200/1590644718.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="25.5" customHeight="1" s="9">
       <c r="A4" s="2" t="n">
@@ -875,7 +883,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P4" s="19" t="n"/>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/74/11/45/1200x1200/1603847351.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="25.5" customHeight="1" s="9">
       <c r="A5" s="2" t="n">
@@ -936,7 +948,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P5" s="19" t="n"/>
+      <c r="P5" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/50/67/61/67/1200x1200/1623184900.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="25.5" customHeight="1" s="9">
       <c r="A6" s="2" t="n">
@@ -997,7 +1013,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P6" s="19" t="n"/>
+      <c r="P6" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/65/28/67/1200x1200/1602057090.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="9">
       <c r="A7" s="2" t="n">
@@ -1062,7 +1082,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P7" s="19" t="n"/>
+      <c r="P7" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/65/53/09/1200x1200/1602106805.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="25.5" customHeight="1" s="9">
       <c r="A8" s="2" t="n">
@@ -1123,7 +1147,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P8" s="19" t="n"/>
+      <c r="P8" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/18/01/49/52/07/75/360x266/1599173160.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="9">
       <c r="A9" s="2" t="n">
@@ -1253,7 +1281,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P10" s="19" t="n"/>
+      <c r="P10" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/57/92/31/1200x1200/1600490803.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="38.25" customHeight="1" s="9">
       <c r="A11" s="2" t="n">
@@ -1318,7 +1350,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P11" s="19" t="n"/>
+      <c r="P11" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/50/11/21/02/1200x1200/1611411915.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="25.5" customHeight="1" s="9">
       <c r="A12" s="2" t="n">
@@ -1379,7 +1415,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P12" s="19" t="n"/>
+      <c r="P12" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/20/41/93/1200x1200/1592569753.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="25.5" customHeight="1" s="9">
       <c r="A13" s="2" t="n">
@@ -1440,7 +1480,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P13" s="19" t="n"/>
+      <c r="P13" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/45/46/72/21/1200x1200/1504957360.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="25.5" customHeight="1" s="9">
       <c r="A14" s="2" t="n">
@@ -1505,7 +1549,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P14" s="19" t="n"/>
+      <c r="P14" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/00/91/10/54/16/1200x1200/1114614444.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="25.5" customHeight="1" s="9">
       <c r="A15" s="2" t="n">
@@ -1566,7 +1614,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P15" s="19" t="n"/>
+      <c r="P15" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/60/70/64/1200x1200/1621653553.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="25.5" customHeight="1" s="9">
       <c r="A16" s="2" t="n">
@@ -1753,7 +1805,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P18" s="19" t="n"/>
+      <c r="P18" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/64/65/02/1200x1200/1601934402.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="25.5" customHeight="1" s="9">
       <c r="A19" s="2" t="n">
@@ -1814,7 +1870,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P19" s="19" t="n"/>
+      <c r="P19" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/46/80/92/11/1200x1200/1586532946.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="25.5" customHeight="1" s="9">
       <c r="A20" s="2" t="n">
@@ -1875,7 +1935,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P20" s="19" t="n"/>
+      <c r="P20" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/50/24/55/38/1200x1200/1614080409.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="25.5" customHeight="1" s="9">
       <c r="A21" s="2" t="n">
@@ -1940,7 +2004,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P21" s="19" t="n"/>
+      <c r="P21" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/48/20/12/18/1200x1200/1601440423.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="25.5" customHeight="1" s="9">
       <c r="A22" s="2" t="n">
@@ -2001,7 +2069,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P22" s="19" t="n"/>
+      <c r="P22" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/48/19/18/21/1200x1200/1601444774.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="25.5" customHeight="1" s="9">
       <c r="A23" s="2" t="n">
@@ -2062,7 +2134,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P23" s="19" t="n"/>
+      <c r="P23" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/45/27/42/86/1200x1200/1624853443.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="25.5" customHeight="1" s="9">
       <c r="A24" s="2" t="n">
@@ -2123,7 +2199,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P24" s="19" t="n"/>
+      <c r="P24" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/46/61/53/66/1200x1200/1578338508.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="25.5" customHeight="1" s="9">
       <c r="A25" s="2" t="n">
@@ -2180,7 +2260,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P25" s="19" t="n"/>
+      <c r="P25" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/48/98/33/90/1200x1200/1588238517.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="25.5" customHeight="1" s="9">
       <c r="A26" s="2" t="n">
@@ -2241,7 +2325,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P26" s="19" t="n"/>
+      <c r="P26" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/46/26/84/79/1200x1200/1590095756.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="25.5" customHeight="1" s="9">
       <c r="A27" s="2" t="n">
@@ -2302,7 +2390,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P27" s="19" t="n"/>
+      <c r="P27" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/45/22/98/98/1200x1200/1561323415.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="25.5" customHeight="1" s="9">
       <c r="A28" s="2" t="n">
@@ -2363,7 +2455,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P28" s="19" t="n"/>
+      <c r="P28" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/18/01/50/51/18/37/360x266/1619879156.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="25.5" customHeight="1" s="9">
       <c r="A29" s="2" t="n">
@@ -2424,7 +2520,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P29" s="19" t="n"/>
+      <c r="P29" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/50/62/78/21/1200x1200/1622151517.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="25.5" customHeight="1" s="9">
       <c r="A30" s="2" t="n">
@@ -2485,7 +2585,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P30" s="19" t="n"/>
+      <c r="P30" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/38/29/29/1200x1200/1596302391.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="25.5" customHeight="1" s="9">
       <c r="A31" s="2" t="n">
@@ -2607,7 +2711,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P32" s="19" t="n"/>
+      <c r="P32" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/49/32/53/03/1200x1200/1595139090.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="25.5" customHeight="1" s="9">
       <c r="A33" s="2" t="n">
@@ -2729,7 +2837,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P34" s="19" t="n"/>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/48/77/63/81/1200x1200/1584238159.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="25.5" customHeight="1" s="9">
       <c r="A35" s="2" t="n">
@@ -2851,7 +2963,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P36" s="19" t="n"/>
+      <c r="P36" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/46/26/99/01/1200x1200/1527813686.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="25.5" customHeight="1" s="9">
       <c r="A37" s="2" t="n">
@@ -2912,7 +3028,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P37" s="19" t="n"/>
+      <c r="P37" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/47/44/77/51/1200x1200/1556642759.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" s="9">
       <c r="A38" s="2" t="n">
@@ -2973,7 +3093,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P38" s="19" t="n"/>
+      <c r="P38" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/18/01/48/70/21/44/360x266/1582831439.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" s="9">
       <c r="A39" s="2" t="n">
@@ -3034,7 +3158,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P39" s="19" t="n"/>
+      <c r="P39" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/47/44/77/51/1200x1200/1556642759.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" s="9">
       <c r="A40" s="2" t="n">
@@ -3095,7 +3223,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P40" s="19" t="n"/>
+      <c r="P40" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/46/78/57/70/1200x1200/1540402288.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" s="9">
       <c r="A41" s="2" t="n">
@@ -3156,7 +3288,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P41" s="19" t="n"/>
+      <c r="P41" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/resize/18/01/50/62/43/55/1200x1200/1622077922.jpg?isFirstImage=true</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" s="9">
       <c r="A42" s="2" t="n">
@@ -3221,7 +3357,11 @@
           <t>Ver listado</t>
         </is>
       </c>
-      <c r="P42" s="19" t="n"/>
+      <c r="P42" s="19" t="inlineStr">
+        <is>
+          <t>https://img10.naventcdn.com/avisos/18/01/50/54/56/94/360x266/1620529487.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="25.5" customHeight="1" s="9">
       <c r="A43" s="2" t="n">
